--- a/data/valuebets_database_2025-07-09.xlsx
+++ b/data/valuebets_database_2025-07-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>09/07 19:00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>100</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45847.07843672411</v>
+        <v>45847.07843672454</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>11/07 16:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>60</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45847.07843672411</v>
+        <v>45847.07843672454</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>12/07 14:00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>60</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45847.07843672411</v>
+        <v>45847.07843672454</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>12/07 21:00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>50</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45847.07843672411</v>
+        <v>45847.07843672454</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>11/07 21:30</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>55</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45847.07843672411</v>
+        <v>45847.07843672454</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>12/07 19:00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>45</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45847.07843672411</v>
+        <v>45847.07843672454</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>09/07 13:10</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>5.20</t>
-        </is>
+      <c r="F8" t="n">
+        <v>5.2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45847.07843672411</v>
+        <v>45847.07843672454</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>09/07 19:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="F9" t="n">
+        <v>3.1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45847.07843672411</v>
+        <v>45847.07843672454</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>12/07 18:30</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>40</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45847.07843672411</v>
+        <v>45847.07843672454</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>12/07 15:30</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>50</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45847.07843672411</v>
+        <v>45847.07843672454</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>09/07 23:30</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>2</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45847.07843672411</v>
+        <v>45847.07843672454</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>09/07 17:30</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
+      <c r="F13" t="n">
+        <v>1.2</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45847.07843672411</v>
+        <v>45847.07843672454</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>09/07 15:00</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>20</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45847.07843672411</v>
+        <v>45847.07843672454</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>09/07 17:30</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
+      <c r="F15" t="n">
+        <v>1.04</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45847.07843672411</v>
+        <v>45847.07843672454</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>14/07 19:15</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>40</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45847.07843672411</v>
+        <v>45847.07843672454</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>09/07 03:00</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
+      <c r="F17" t="n">
+        <v>1.52</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,142 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45847.07843672411</v>
+        <v>45847.07843672454</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 25.5 - tirs | Paris SG –</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Paris SG – Real MadridCoupe du Monde des Clubs</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Moins que 25.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>09/07 19:00</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>40,4%</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>+15,1%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>45847.14170919588</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Club Améri</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Club América – Club TijuanaLiga MX</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>17/07 01:00</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>+4,85%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>45847.14170919588</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Shelbourne</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Shelbourne FC – LinfieldLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>09/07 18:45</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>+2,11%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>45847.14170919588</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-09.xlsx
+++ b/data/valuebets_database_2025-07-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1193,10 +1193,8 @@
           <t>09/07 19:00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
+      <c r="F18" t="n">
+        <v>2.85</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1209,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45847.14170919588</v>
+        <v>45847.14170920139</v>
       </c>
     </row>
     <row r="19">
@@ -1238,10 +1236,8 @@
           <t>17/07 01:00</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>45</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1254,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45847.14170919588</v>
+        <v>45847.14170920139</v>
       </c>
     </row>
     <row r="20">
@@ -1283,10 +1279,8 @@
           <t>09/07 18:45</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>45</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1299,7 +1293,232 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45847.14170919588</v>
+        <v>45847.14170920139</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 25.5 - tirs | Paris SG –</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Paris SG – Real MadridInternational - Coupe du Monde des Clubs 2025</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Moins que 25.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>09/07 19:00</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>40,4%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>+21,1%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>45847.19205154554</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | X2 | Ludogorets</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ludogorets – Dinamo MinskEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>09/07 17:30</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>27,0%</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>+3,84%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>45847.19205154554</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis | Plus que 12.51er participant | Salisbury/</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Salisbury/Skupski – Granollers/ZeballosWimbledon 2025 - Hommes</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Plus que 12.51er participant</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>09/07 12:00</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>59,5%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>+1,15%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>45847.19205154554</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | 2 | Shelbourne</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Shelbourne – LinfieldEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>09/07 18:45</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>24,0%</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>+0,72%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>45847.19205154554</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Football | 1X2e période | France – P</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Football</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>France – Pays de GallesInternational - Euro 2025 (F)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1X2e période</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>09/07 19:00</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>96,2%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>+0,08%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>45847.19205154554</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-09.xlsx
+++ b/data/valuebets_database_2025-07-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1322,10 +1322,8 @@
           <t>09/07 19:00</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>3</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1338,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45847.19205154554</v>
+        <v>45847.19205155093</v>
       </c>
     </row>
     <row r="22">
@@ -1367,10 +1365,8 @@
           <t>09/07 17:30</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>3.85</t>
-        </is>
+      <c r="F22" t="n">
+        <v>3.85</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1383,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45847.19205154554</v>
+        <v>45847.19205155093</v>
       </c>
     </row>
     <row r="23">
@@ -1412,10 +1408,8 @@
           <t>09/07 12:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
+      <c r="F23" t="n">
+        <v>1.7</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1428,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45847.19205154554</v>
+        <v>45847.19205155093</v>
       </c>
     </row>
     <row r="24">
@@ -1457,10 +1451,8 @@
           <t>09/07 18:45</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="F24" t="n">
+        <v>4.2</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1473,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45847.19205154554</v>
+        <v>45847.19205155093</v>
       </c>
     </row>
     <row r="25">
@@ -1502,10 +1494,8 @@
           <t>09/07 19:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
+      <c r="F25" t="n">
+        <v>1.04</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1518,7 +1508,52 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45847.19205154554</v>
+        <v>45847.19205155093</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | Flavio Cob</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Flavio Cobolli – Novak DjokovicATP - Wimbledon</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>09/07 13:40</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>82,9%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>+11,9%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>45847.22713715675</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-09.xlsx
+++ b/data/valuebets_database_2025-07-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1537,10 +1537,8 @@
           <t>09/07 13:40</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
+      <c r="F26" t="n">
+        <v>1.35</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1553,7 +1551,52 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45847.22713715675</v>
+        <v>45847.22713715277</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | France – P</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>France – Pays de GallesUEFA Euro (F) - Matchs</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>09/07 19:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+488%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45847.27372344503</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-09.xlsx
+++ b/data/valuebets_database_2025-07-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>09/07 19:00</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>200</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,97 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45847.27372344503</v>
+        <v>45847.27372344907</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 21-2- se qualifie | Shelbourne</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Shelbourne FC – Linfield FC385076e7 Europe. Ligue des Champions (Q)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>21-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>09/07 18:45</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>53,0%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+0,70%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45847.30767464894</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | Iga Swiate</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Iga Swiatek – Ludmilla SamsonovaWTA - Wimbledon</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>09/07 12:00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>42,6%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+0,18%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45847.30767464894</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-09.xlsx
+++ b/data/valuebets_database_2025-07-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1623,10 +1623,8 @@
           <t>09/07 18:45</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
+      <c r="F28" t="n">
+        <v>1.9</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1639,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45847.30767464894</v>
+        <v>45847.30767465278</v>
       </c>
     </row>
     <row r="29">
@@ -1668,10 +1666,8 @@
           <t>09/07 12:00</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
+      <c r="F29" t="n">
+        <v>2.35</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1684,7 +1680,187 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45847.30767464894</v>
+        <v>45847.30767465278</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.51re équipe | Pologne – </t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Pologne – DanemarkUEFA Euro (F) - Matchs</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>12/07 19:00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+13,7%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45847.35478068566</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Remplaçant marque un but: Oui | Paris SG –</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Paris SG – Real MadridCoupe du Monde des Clubs</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Remplaçant marque un but: Oui</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>09/07 19:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>42,6%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+6,60%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45847.35478068566</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | 21re période | FCSB – Int</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>FCSB – Inter Club de EscaldesEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>21re période</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>09/07 17:30</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>28.50</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>3,68%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+4,85%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45847.35478068566</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | 1X | Shelbourne</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Shelbourne – LinfieldEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>09/07 18:45</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>77,0%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+0,09%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45847.35478068566</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-09.xlsx
+++ b/data/valuebets_database_2025-07-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1709,10 +1709,8 @@
           <t>12/07 19:00</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>50</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1725,7 +1723,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45847.35478068566</v>
+        <v>45847.35478068287</v>
       </c>
     </row>
     <row r="31">
@@ -1754,10 +1752,8 @@
           <t>09/07 19:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F31" t="n">
+        <v>2.5</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1770,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45847.35478068566</v>
+        <v>45847.35478068287</v>
       </c>
     </row>
     <row r="32">
@@ -1799,10 +1795,8 @@
           <t>09/07 17:30</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>28.50</t>
-        </is>
+      <c r="F32" t="n">
+        <v>28.5</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1815,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45847.35478068566</v>
+        <v>45847.35478068287</v>
       </c>
     </row>
     <row r="33">
@@ -1844,10 +1838,8 @@
           <t>09/07 18:45</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
+      <c r="F33" t="n">
+        <v>1.3</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1860,7 +1852,97 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45847.35478068566</v>
+        <v>45847.35478068287</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Moins que 25.5 - tirs | Paris SG –</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Paris SG – Real MadridInternational - CDM des Clubs</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Moins que 25.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>09/07 19:00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>39,5%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+8,49%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45847.3936217559</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Football | 11-2- se qualifie | VMFD Zalgi</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Football</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>VMFD Zalgiris – Hamrun Spartans FCLigue des Champions UEFA - Éliminatoires</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>11-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>09/07 16:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>56,2%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+0,06%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45847.3936217559</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-09.xlsx
+++ b/data/valuebets_database_2025-07-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1881,10 +1881,8 @@
           <t>09/07 19:00</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F34" t="n">
+        <v>2.75</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1897,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45847.3936217559</v>
+        <v>45847.39362175926</v>
       </c>
     </row>
     <row r="35">
@@ -1926,10 +1924,8 @@
           <t>09/07 16:00</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
+      <c r="F35" t="n">
+        <v>1.78</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1942,7 +1938,142 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45847.3936217559</v>
+        <v>45847.39362175926</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 5.5 - tir cadré1re équipe | Angleterre</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Angleterre F. – Pays-Bas F.Europe - Euro Féminin 2025</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Plus que 5.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>09/07 16:00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>45,7%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+8,34%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45847.43455813698</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Moins que 5.51er set1er participant | Jannik Sin</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Jannik Sinner – Ben SheltonWimbledon (H)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Moins que 5.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>09/07 13:10</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>23,1%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+3,98%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45847.43455813698</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | 1X | Žalgiris –</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Žalgiris – Hamrun SpartansEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>09/07 16:00</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>83,4%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+0,03%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45847.43455813698</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-09.xlsx
+++ b/data/valuebets_database_2025-07-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1967,10 +1967,8 @@
           <t>09/07 16:00</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2.37</t>
-        </is>
+      <c r="F36" t="n">
+        <v>2.37</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1983,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45847.43455813698</v>
+        <v>45847.43455813657</v>
       </c>
     </row>
     <row r="37">
@@ -2012,10 +2010,8 @@
           <t>09/07 13:10</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="F37" t="n">
+        <v>4.5</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2028,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45847.43455813698</v>
+        <v>45847.43455813657</v>
       </c>
     </row>
     <row r="38">
@@ -2057,10 +2053,8 @@
           <t>09/07 16:00</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
+      <c r="F38" t="n">
+        <v>1.2</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2073,7 +2067,97 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45847.43455813698</v>
+        <v>45847.43455813657</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | Moins que 23.5 - aces | Jannik Sin</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Jannik Sinner – Ben SheltonATP - Wimbledon</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Moins que 23.5 - aces</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>09/07 13:10</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>44,7%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+2,90%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45847.47235836425</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 8.5 - tir cadré | New Englan</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>New England Revolution – Inter Miami CFÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Moins que 8.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>09/07 23:30</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>37,5%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+1,15%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45847.47235836425</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-09.xlsx
+++ b/data/valuebets_database_2025-07-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2096,10 +2096,8 @@
           <t>09/07 13:10</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="F39" t="n">
+        <v>2.3</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2112,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45847.47235836425</v>
+        <v>45847.47235836805</v>
       </c>
     </row>
     <row r="40">
@@ -2141,10 +2139,8 @@
           <t>09/07 23:30</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F40" t="n">
+        <v>2.7</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2157,7 +2153,97 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45847.47235836425</v>
+        <v>45847.47235836805</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PokerStars(FR)Basketball | X3e période[race to 15 regular time] | Minnesota </t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Minnesota Lynx – Phoenix MercuryUSA - WNBA</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>X3e période[race to 15 regular time]</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>09/07 19:30</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>4,07%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+1,82%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45847.53241526521</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 2 - tir cadré | Angleterre</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Angleterre (F) – Pays-Bas (F)Europe. UEFA Euro 2025 (F)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>09/07 16:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>29,9%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+1,69%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45847.53241526521</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-09.xlsx
+++ b/data/valuebets_database_2025-07-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2182,10 +2182,8 @@
           <t>09/07 19:30</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>25.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>25</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2198,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45847.53241526521</v>
+        <v>45847.53241526621</v>
       </c>
     </row>
     <row r="42">
@@ -2227,10 +2225,8 @@
           <t>09/07 16:00</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="F42" t="n">
+        <v>3.4</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2243,7 +2239,97 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45847.53241526521</v>
+        <v>45847.53241526621</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | AIK – Dege</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AIK – Degerfors IFAllsvenskan</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>13/07 14:30</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+27,2%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45847.56631662569</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 14.5 - tirs1re équipe | Angleterre</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Angleterre F. – Pays-Bas F.Europe - Euro Féminin 2025</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Plus que 14.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>09/07 16:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>47,3%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+4,05%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45847.56631662569</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-09.xlsx
+++ b/data/valuebets_database_2025-07-09.xlsx
@@ -2268,10 +2268,8 @@
           <t>13/07 14:30</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F43" t="n">
+        <v>60</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2284,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45847.56631662569</v>
+        <v>45847.56631662037</v>
       </c>
     </row>
     <row r="44">
@@ -2313,10 +2311,8 @@
           <t>09/07 16:00</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="F44" t="n">
+        <v>2.2</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2329,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45847.56631662569</v>
+        <v>45847.56631662037</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-09.xlsx
+++ b/data/valuebets_database_2025-07-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2328,6 +2328,141 @@
         <v>45847.56631662037</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | X2 | FCSB – Int</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>FCSB – Inter Club De EscaldesEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>09/07 17:30</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>8,60%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+3,22%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45847.64248662919</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Volleyball | H 2 (+4.5)1er set | Italie (F)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Volleyball</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Italie (F) – Serbie (F)International - Ligue des Nations (F)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>H 2 (+4.5)1er set</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>10/07 15:00</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>47,2%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+1,53%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45847.64248662919</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | 11-2- se qualifie | Žalgiris –</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Žalgiris – Hamrun SpartansEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>11-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>09/07 16:00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>59,0%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+0,25%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45847.64248662919</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-07-09.xlsx
+++ b/data/valuebets_database_2025-07-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2354,10 +2354,8 @@
           <t>09/07 17:30</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>12.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>12</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2370,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45847.64248662919</v>
+        <v>45847.64248663194</v>
       </c>
     </row>
     <row r="46">
@@ -2399,10 +2397,8 @@
           <t>10/07 15:00</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="F46" t="n">
+        <v>2.15</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2415,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45847.64248662919</v>
+        <v>45847.64248663194</v>
       </c>
     </row>
     <row r="47">
@@ -2444,10 +2440,8 @@
           <t>09/07 16:00</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
+      <c r="F47" t="n">
+        <v>1.7</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2460,7 +2454,52 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45847.64248662919</v>
+        <v>45847.64248663194</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | 22e période | FCSB – Int</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>FCSB – Inter Club de EscaldesEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>22e période</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>09/07 17:30</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>24.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>4,99%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+19,7%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45847.68608671745</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-09.xlsx
+++ b/data/valuebets_database_2025-07-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2483,10 +2483,8 @@
           <t>09/07 17:30</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>24.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>24</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2499,7 +2497,142 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45847.68608671745</v>
+        <v>45847.68608671297</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Internacio</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Internacional – Vitoria BASérie A</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>12/07 19:30</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+23,9%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45847.72341888139</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 11-2- se qualifie | Shakhtar D</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Shakhtar Donetsk – Ilves TampereEurope. Europa League (Q)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>11-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>10/07 18:00</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>91,0%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+0,15%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45847.72341888139</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Plus que 0.5 | Ludogorets</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ludogorets – Dinamo MinskEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Plus que 0.5</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>09/07 17:30</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>95,3%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+0,01%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45847.72341888139</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-09.xlsx
+++ b/data/valuebets_database_2025-07-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2526,10 +2526,8 @@
           <t>12/07 19:30</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F49" t="n">
+        <v>60</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2542,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45847.72341888139</v>
+        <v>45847.72341887731</v>
       </c>
     </row>
     <row r="50">
@@ -2571,10 +2569,8 @@
           <t>10/07 18:00</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>1.10</t>
-        </is>
+      <c r="F50" t="n">
+        <v>1.1</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2587,7 +2583,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45847.72341888139</v>
+        <v>45847.72341887731</v>
       </c>
     </row>
     <row r="51">
@@ -2616,10 +2612,8 @@
           <t>09/07 17:30</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
+      <c r="F51" t="n">
+        <v>1.05</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2632,7 +2626,97 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45847.72341888139</v>
+        <v>45847.72341887731</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 21-2- se qualifie | Spartak Tr</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Spartak Trnava – BK HäckenEurope. Europa League (Q)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>21-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>10/07 18:15</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>61,0%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+1,23%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45847.77274757127</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | 1X | Internacio</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Internacional – VitoriaBrésil - Serie A</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>12/07 19:30</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>83,4%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+0,04%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45847.77274757127</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-09.xlsx
+++ b/data/valuebets_database_2025-07-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2655,10 +2655,8 @@
           <t>10/07 18:15</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
+      <c r="F52" t="n">
+        <v>1.66</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2671,7 +2669,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45847.77274757127</v>
+        <v>45847.77274756944</v>
       </c>
     </row>
     <row r="53">
@@ -2700,10 +2698,8 @@
           <t>12/07 19:30</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
+      <c r="F53" t="n">
+        <v>1.2</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2716,7 +2712,97 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45847.77274757127</v>
+        <v>45847.77274756944</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>PMU(FR)Tennis | H 2 (−7.5) | Fritz, Tay</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>PMU(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Fritz, Taylor – Alcaraz, CarlosEvénements. Wimbledon (H)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>H 2 (−7.5)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>11/07 00:00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>27,0%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+5,32%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45847.80478674886</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Volleyball | 11-21er set[race to 10 regular time] | Corée du S</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Volleyball</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Corée du Sud F. – Japon F.International - Ligue des nations F.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>11-21er set[race to 10 regular time]</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>10/07 10:20</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>4.45</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>22,7%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+1,17%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45847.80478674886</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-09.xlsx
+++ b/data/valuebets_database_2025-07-09.xlsx
@@ -2741,10 +2741,8 @@
           <t>11/07 00:00</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
+      <c r="F54" t="n">
+        <v>3.9</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2757,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45847.80478674886</v>
+        <v>45847.80478674769</v>
       </c>
     </row>
     <row r="55">
@@ -2786,10 +2784,8 @@
           <t>10/07 10:20</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>4.45</t>
-        </is>
+      <c r="F55" t="n">
+        <v>4.45</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2802,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45847.80478674886</v>
+        <v>45847.80478674769</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-09.xlsx
+++ b/data/valuebets_database_2025-07-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2801,6 +2801,51 @@
         <v>45847.80478674769</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Volleyball | H 2 (−19.5) | France – B</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Volleyball</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>France – BrésilLigue des Nations (F)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>H 2 (−19.5)</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>10/07 06:30</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>46,0%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+2,12%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45847.88986289354</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-07-09.xlsx
+++ b/data/valuebets_database_2025-07-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2827,10 +2827,8 @@
           <t>10/07 06:30</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
+      <c r="F56" t="n">
+        <v>2.22</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2843,7 +2841,142 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45847.88986289354</v>
+        <v>45847.88986289352</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betsson(FR)Football | H 2 (+0.5) | Norvège – </t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Football</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Norvège – IslandeInternational - Euro 2025 (F)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>H 2 (+0.5)</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>10/07 19:00</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>56,7%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+1,00%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45847.93196040139</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Club Boliv</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Club Bolivar – PalestinoCopa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>16/07 22:00</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+0,94%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45847.93196040139</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Volleyball | Moins que 3.5 | France – B</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Volleyball</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>France – BrésilLigue des Nations (F)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Moins que 3.5</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>10/07 06:30</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>64,6%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+0,17%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45847.93196040139</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-09.xlsx
+++ b/data/valuebets_database_2025-07-09.xlsx
@@ -2870,10 +2870,8 @@
           <t>10/07 19:00</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
+      <c r="F57" t="n">
+        <v>1.78</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2886,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45847.93196040139</v>
+        <v>45847.93196040509</v>
       </c>
     </row>
     <row r="58">
@@ -2915,10 +2913,8 @@
           <t>16/07 22:00</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F58" t="n">
+        <v>50</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2931,7 +2927,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45847.93196040139</v>
+        <v>45847.93196040509</v>
       </c>
     </row>
     <row r="59">
@@ -2960,10 +2956,8 @@
           <t>10/07 06:30</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
+      <c r="F59" t="n">
+        <v>1.55</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2976,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45847.93196040139</v>
+        <v>45847.93196040509</v>
       </c>
     </row>
   </sheetData>
